--- a/src/test/resources/testdata/SauceDemoTestData.xlsx
+++ b/src/test/resources/testdata/SauceDemoTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\_________________TREE_________________________\FINAL_SHECDULE_TRAINING\Week_6\playwright-java-cucumber-jenkins-jira-framework\tclife\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B873E08B-5630-454E-8AD4-6565FCD93D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A002C2E-ECF0-4080-B2DA-9586E6B2B509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12075" yWindow="7410" windowWidth="43200" windowHeight="23415" xr2:uid="{A7E215A2-736B-4DED-8E9E-CE8C4568D4BB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>username</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Epic sadface: Sorry, this user has been locked ou</t>
-  </si>
-  <si>
-    <t>secret_sauce1</t>
   </si>
 </sst>
 </file>
@@ -435,7 +432,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
